--- a/artfynd/A 45369-2025 artfynd.xlsx
+++ b/artfynd/A 45369-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129533314</v>
       </c>
       <c r="B2" t="n">
-        <v>90983</v>
+        <v>90986</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129533317</v>
       </c>
       <c r="B3" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129533319</v>
       </c>
       <c r="B4" t="n">
-        <v>96970</v>
+        <v>96973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,6 +1012,347 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129592452</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Marsjön, Marsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>597942</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6536797</v>
+      </c>
+      <c r="S5" t="n">
+        <v>14</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Årdala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129592464</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92847</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Marsjön, Marsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>597941</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6536665</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Årdala</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129592469</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96216</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Marsjön, Marsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>597955</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6536655</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Årdala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45369-2025 artfynd.xlsx
+++ b/artfynd/A 45369-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129533314</v>
       </c>
       <c r="B2" t="n">
-        <v>90986</v>
+        <v>91014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129533317</v>
       </c>
       <c r="B3" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129533319</v>
       </c>
       <c r="B4" t="n">
-        <v>96973</v>
+        <v>97002</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>129592464</v>
       </c>
       <c r="B6" t="n">
-        <v>92847</v>
+        <v>92875</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>129592469</v>
       </c>
       <c r="B7" t="n">
-        <v>96216</v>
+        <v>96245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45369-2025 artfynd.xlsx
+++ b/artfynd/A 45369-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129533314</v>
       </c>
       <c r="B2" t="n">
-        <v>91014</v>
+        <v>91020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129533317</v>
       </c>
       <c r="B3" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129533319</v>
       </c>
       <c r="B4" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>129592464</v>
       </c>
       <c r="B6" t="n">
-        <v>92875</v>
+        <v>92881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>129592469</v>
       </c>
       <c r="B7" t="n">
-        <v>96245</v>
+        <v>96257</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45369-2025 artfynd.xlsx
+++ b/artfynd/A 45369-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129533314</v>
       </c>
       <c r="B2" t="n">
-        <v>91020</v>
+        <v>91021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129533317</v>
       </c>
       <c r="B3" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129533319</v>
       </c>
       <c r="B4" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>129592464</v>
       </c>
       <c r="B6" t="n">
-        <v>92881</v>
+        <v>92882</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>129592469</v>
       </c>
       <c r="B7" t="n">
-        <v>96257</v>
+        <v>96258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45369-2025 artfynd.xlsx
+++ b/artfynd/A 45369-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129533314</v>
       </c>
       <c r="B2" t="n">
-        <v>91021</v>
+        <v>91026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129533317</v>
       </c>
       <c r="B3" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129533319</v>
       </c>
       <c r="B4" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>129592464</v>
       </c>
       <c r="B6" t="n">
-        <v>92882</v>
+        <v>92887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>129592469</v>
       </c>
       <c r="B7" t="n">
-        <v>96258</v>
+        <v>96263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45369-2025 artfynd.xlsx
+++ b/artfynd/A 45369-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129533314</v>
       </c>
       <c r="B2" t="n">
-        <v>91026</v>
+        <v>91030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129533317</v>
       </c>
       <c r="B3" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129533319</v>
       </c>
       <c r="B4" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>129592464</v>
       </c>
       <c r="B6" t="n">
-        <v>92887</v>
+        <v>92891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>129592469</v>
       </c>
       <c r="B7" t="n">
-        <v>96263</v>
+        <v>96267</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45369-2025 artfynd.xlsx
+++ b/artfynd/A 45369-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129533314</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>91032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129533317</v>
       </c>
       <c r="B3" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129533319</v>
       </c>
       <c r="B4" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>129592464</v>
       </c>
       <c r="B6" t="n">
-        <v>92891</v>
+        <v>92893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>129592469</v>
       </c>
       <c r="B7" t="n">
-        <v>96267</v>
+        <v>96269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45369-2025 artfynd.xlsx
+++ b/artfynd/A 45369-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>129533319</v>
       </c>
       <c r="B4" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>129592469</v>
       </c>
       <c r="B7" t="n">
-        <v>96269</v>
+        <v>96279</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45369-2025 artfynd.xlsx
+++ b/artfynd/A 45369-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129533314</v>
       </c>
       <c r="B2" t="n">
-        <v>91032</v>
+        <v>91035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129533317</v>
       </c>
       <c r="B3" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129533319</v>
       </c>
       <c r="B4" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>129592464</v>
       </c>
       <c r="B6" t="n">
-        <v>92893</v>
+        <v>92896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>129592469</v>
       </c>
       <c r="B7" t="n">
-        <v>96279</v>
+        <v>96283</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45369-2025 artfynd.xlsx
+++ b/artfynd/A 45369-2025 artfynd.xlsx
@@ -1133,7 +1133,7 @@
         <v>129592464</v>
       </c>
       <c r="B6" t="n">
-        <v>92896</v>
+        <v>92899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>129592469</v>
       </c>
       <c r="B7" t="n">
-        <v>96283</v>
+        <v>96286</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
